--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499926.0487133448</v>
+        <v>499926</v>
       </c>
       <c r="R2" t="n">
-        <v>6373043.936535051</v>
+        <v>6373044</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7898-2025 artfynd.xlsx
+++ b/artfynd/A 7898-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153438</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
